--- a/verification/cases/roundtrip/mixed_sheets/init.xlsx
+++ b/verification/cases/roundtrip/mixed_sheets/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23206"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D28FE986-BB72-4B57-B79A-527E619AF766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17540" windowHeight="11760" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -66,7 +72,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -181,7 +187,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -235,6 +241,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -561,15 +570,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="12.75" customHeight="1">
+    <row r="1" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,7 +586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="12.75" customHeight="1">
+    <row r="2" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -597,14 +606,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.75" customHeight="1">
+    <row r="1" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -615,7 +624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="12.75" customHeight="1">
+    <row r="2" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -626,7 +635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="12.75" customHeight="1">
+    <row r="3" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -648,14 +657,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="12.75" customHeight="1">
+    <row r="1" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -663,7 +672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="12.75" customHeight="1">
+    <row r="2" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -671,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="12.75" customHeight="1">
+    <row r="3" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
   </sheetData>
